--- a/output/docs/DOC_068_SAST_report.xlsx
+++ b/output/docs/DOC_068_SAST_report.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>sample_app/app.py:9</t>
+          <t>./sample_app/app.py:9</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>sample_app/app.py:12</t>
+          <t>./sample_app/app.py:12</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>sample_app/app.py:17</t>
+          <t>./sample_app/app.py:17</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>sample_app/app.py:23</t>
+          <t>./sample_app/app.py:23</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>sample_app/app.py:30</t>
+          <t>./sample_app/app.py:30</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>sample_app/app.py:35</t>
+          <t>./sample_app/app.py:35</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>sample_app/app.py:40</t>
+          <t>./sample_app/app.py:40</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>sample_app/app.py:46</t>
+          <t>./sample_app/app.py:46</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
